--- a/outputs/q1/final/q1_final_delivery.xlsx
+++ b/outputs/q1/final/q1_final_delivery.xlsx
@@ -37883,7 +37883,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.1</v>
+        <v>0.108305</v>
       </c>
       <c r="AJ2" t="n">
         <v>5742</v>
@@ -38267,7 +38267,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.090115</v>
+        <v>0.090338</v>
       </c>
       <c r="AJ2" t="n">
         <v>5742</v>
@@ -38417,7 +38417,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.08298899999999999</v>
+        <v>0.090237</v>
       </c>
       <c r="AJ3" t="n">
         <v>5742</v>
@@ -38575,7 +38575,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.111119</v>
+        <v>0.117693</v>
       </c>
       <c r="AJ4" t="n">
         <v>5742</v>
@@ -38733,7 +38733,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.104103</v>
+        <v>0.11462</v>
       </c>
       <c r="AJ5" t="n">
         <v>5742</v>
@@ -38891,7 +38891,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.097159</v>
+        <v>0.09633899999999999</v>
       </c>
       <c r="AJ6" t="n">
         <v>5742</v>
@@ -39049,7 +39049,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.099326</v>
+        <v>0.104201</v>
       </c>
       <c r="AJ7" t="n">
         <v>5742</v>
@@ -39207,7 +39207,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.157814</v>
+        <v>0.153386</v>
       </c>
       <c r="AJ8" t="n">
         <v>5742</v>
@@ -39365,7 +39365,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.118351</v>
+        <v>0.124917</v>
       </c>
       <c r="AJ9" t="n">
         <v>5742</v>
@@ -39523,7 +39523,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.11111</v>
+        <v>0.138773</v>
       </c>
       <c r="AJ10" t="n">
         <v>5742</v>
@@ -39681,7 +39681,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.137941</v>
+        <v>0.145732</v>
       </c>
       <c r="AJ11" t="n">
         <v>5742</v>
@@ -40100,7 +40100,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.097188</v>
+        <v>0.09771299999999999</v>
       </c>
       <c r="AJ2" t="n">
         <v>5742</v>
@@ -40257,7 +40257,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.097473</v>
+        <v>0.103142</v>
       </c>
       <c r="AJ3" t="n">
         <v>5742</v>
@@ -40414,7 +40414,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.132364</v>
+        <v>0.09719800000000001</v>
       </c>
       <c r="AJ4" t="n">
         <v>5742</v>
@@ -40571,7 +40571,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.145537</v>
+        <v>0.104064</v>
       </c>
       <c r="AJ5" t="n">
         <v>5742</v>
@@ -40728,7 +40728,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.104089</v>
+        <v>0.10418</v>
       </c>
       <c r="AJ6" t="n">
         <v>5742</v>
@@ -40885,7 +40885,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09935099999999999</v>
+        <v>0.09729699999999999</v>
       </c>
       <c r="AJ7" t="n">
         <v>5742</v>
@@ -41042,7 +41042,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.097233</v>
+        <v>0.111024</v>
       </c>
       <c r="AJ8" t="n">
         <v>5742</v>
@@ -41203,7 +41203,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.125028</v>
+        <v>0.116834</v>
       </c>
       <c r="AJ9" t="n">
         <v>5742</v>
@@ -41364,7 +41364,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.104352</v>
+        <v>0.104164</v>
       </c>
       <c r="AJ10" t="n">
         <v>5742</v>
@@ -41521,7 +41521,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.082428</v>
+        <v>0.09028</v>
       </c>
       <c r="AJ11" t="n">
         <v>5742</v>
@@ -41678,7 +41678,7 @@
         <v>1e-06</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.06249</v>
+        <v>0.064279</v>
       </c>
       <c r="AJ12" t="n">
         <v>5742</v>
